--- a/bizconfig/static-xlsx/moba/pixel_moba/skill.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/skill.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,74 +645,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>技能ID(5xxx段)</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5001</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>唯一字符串索引,如 archer_q/warrior_r</t>
+          <t>warrior_q</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>冲锋</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>类型: active(主动)/passive(被动)/aura(光环)</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>施法方式: instant/projectile/point/target_aoe</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>伤害类型: physical/magical/true(真实伤害)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>最大等级(固定 9)</t>
-        </is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>触发effect id链,JSON数组如 [1,2],仅服务端</t>
+          <t>[6006]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>客户端图标路径</t>
+          <t>res://gameplay/content/skills/warrior_q/icon.png</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>客户端描述(支持{level}占位符)</t>
+          <t>向前冲刺撞击敌人,施加震荡状态</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>消耗类型: mana/health/none(无消耗)</t>
+          <t>mana</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>warrior_q</t>
+          <t>warrior_w</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>冲锋斩</t>
+          <t>旋风斩</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,7 +718,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>self_persistent_field</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -733,19 +729,14 @@
       <c r="G6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>res://gameplay/content/skills/warrior_q/icon.png</t>
+          <t>res://gameplay/content/skills/warrior_w/icon.png</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>向目标方向冲锋,造成{level}点物理伤害</t>
+          <t>持续旋转攻击周围敌人,对震荡目标伤害提高</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -765,7 +756,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>火球术</t>
+          <t>寒冰领域</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -775,7 +766,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>persistent_field</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -788,7 +779,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[6007]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -798,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>发射火球,造成{level}点法术伤害</t>
+          <t>创建减速区域,叠加寒冷层数</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -809,16 +800,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5021</v>
+        <v>5012</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>archer_q</t>
+          <t>mage_w</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>穿透箭</t>
+          <t>奥术飞弹</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -828,33 +819,357 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>multi_projectile</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>magical</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>9</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[3]</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>res://gameplay/content/skills/mage_w/icon.png</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>发射多发追踪飞弹,寒冷满层触发冻结</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5021</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>archer_q</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>穿透射击</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>piercing_projectile</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[6005]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>res://gameplay/content/skills/archer_q/icon.png</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>射出穿透箭,对路径上敌人造成{level}点物理伤害</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>射出穿透箭矢,施加破甲标记</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>archer_w</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>翻滚射击</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>res://gameplay/content/skills/archer_w/icon.png</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>翻滚并强化下一次普攻</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5003</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>warrior_e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>warrior_e_placeholder</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5004</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>warrior_r</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>warrior_r_placeholder</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5013</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mage_e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mage_e_placeholder</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>magical</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5014</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mage_r</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mage_r_placeholder</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>magical</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>archer_e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>archer_e_placeholder</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>archer_r</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>archer_r_placeholder</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>mana</t>
         </is>
